--- a/Raw_Data/Algae_Cell_count/combine_spat_cell_count.xlsx
+++ b/Raw_Data/Algae_Cell_count/combine_spat_cell_count.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\CSMS_CBP_MassLab\Liel Uziahu\GitHub\Stylophora-pistillata-FPs\Raw_Data\Algae_Cell_count\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CC1237F-875C-4C0A-99BB-A489FF70FA88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05BCB612-9D96-43E4-9EAA-986757EE1C72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4170" yWindow="2760" windowWidth="25785" windowHeight="16920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5070" yWindow="5070" windowWidth="21990" windowHeight="12345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet5" sheetId="5" r:id="rId1"/>
@@ -218,16 +218,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5014,6 +5014,12 @@
       <c r="B103" t="s">
         <v>14</v>
       </c>
+      <c r="C103">
+        <v>1</v>
+      </c>
+      <c r="D103">
+        <v>27</v>
+      </c>
       <c r="E103" s="7">
         <v>8.1999999999999993</v>
       </c>
@@ -5024,9 +5030,9 @@
         <f t="shared" si="3"/>
         <v>95000</v>
       </c>
-      <c r="H103" t="e">
+      <c r="H103">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>95000</v>
       </c>
       <c r="I103">
         <f t="shared" si="5"/>
